--- a/documents/01_設計書/02_データベース設計書_Always First.xlsx
+++ b/documents/01_設計書/02_データベース設計書_Always First.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://seplus2016-my.sharepoint.com/personal/furuhashi-nami-plusdojo2025_seplus2016_onmicrosoft_com/Documents/SEplus/研修/6月チーム開発/提出用/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1021" documentId="13_ncr:1_{86607413-9090-43E4-8B5E-149280F3154D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B7A709E-08B9-4885-9F86-FB84414E746A}"/>
+  <xr:revisionPtr revIDLastSave="1049" documentId="13_ncr:1_{86607413-9090-43E4-8B5E-149280F3154D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{159BDB9D-CFE5-47FB-A5FE-67DAE51D481B}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="4572" yWindow="3396" windowWidth="17280" windowHeight="9960" firstSheet="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="テーブル一覧" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="206">
   <si>
     <t>テーブル一覧</t>
     <rPh sb="4" eb="6">
@@ -82,13 +82,21 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>peace</t>
-  </si>
-  <si>
     <t>作成日</t>
     <rPh sb="0" eb="3">
       <t>サクセイビ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データベース名</t>
+    <rPh sb="6" eb="7">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>a1</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -458,7 +466,10 @@
     <t>CHAR</t>
   </si>
   <si>
-    <t>emoji CHAR (1) NOT NULL,</t>
+    <t>CHARACTER SET utf8mb4をする</t>
+  </si>
+  <si>
+    <t>emoji CHAR (1) CHARACTER SET utf8mb4 NOT NULL,</t>
   </si>
   <si>
     <t>PRIMARY KEY(emotion_id)</t>
@@ -570,9 +581,6 @@
     <t>photo1</t>
   </si>
   <si>
-    <t>BLOB</t>
-  </si>
-  <si>
     <t>×</t>
   </si>
   <si>
@@ -600,7 +608,7 @@
     <t>photo5</t>
   </si>
   <si>
-    <t>photo5 BLOB ,</t>
+    <t>photo5 VARCHAR,</t>
   </si>
   <si>
     <t>PRIMARY KEY(visitor_id),</t>
@@ -664,7 +672,7 @@
     <t>称号名称</t>
   </si>
   <si>
-    <t>name VARCHAR (20)NOT NULL,</t>
+    <t>DR</t>
   </si>
   <si>
     <t>記章画像</t>
@@ -673,7 +681,7 @@
     <t>badge_image</t>
   </si>
   <si>
-    <t>badge_image BLOB NOT NULL,</t>
+    <t>badge_image VARCHAR NOT NULL,</t>
   </si>
   <si>
     <t>PRIMARY KEY(badge_id)</t>
@@ -736,7 +744,7 @@
     <t>gacha_id INT NOT NULL AUTO_INCREMENT,</t>
   </si>
   <si>
-    <t>user_id INT NOT NULL,</t>
+    <t>user_id VARCHAR(255) NOT NULL,</t>
   </si>
   <si>
     <t>回した日</t>
@@ -770,14 +778,7 @@
     <t>ON UPDATE CASCADE</t>
   </si>
   <si>
-    <t>データベース名</t>
-    <rPh sb="6" eb="7">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>a1</t>
+    <t>TABI×TILE</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -819,13 +820,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF181818"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -844,6 +838,13 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -859,7 +860,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -923,13 +924,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -957,19 +982,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1">
@@ -982,6 +1004,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1752,14 +1786,14 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="E3" s="5">
         <v>45820</v>
@@ -1767,74 +1801,74 @@
     </row>
     <row r="4" spans="1:6">
       <c r="B4" s="1" t="s">
-        <v>204</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="D4" s="17" t="s">
         <v>9</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="D5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="17">
+        <v>11</v>
+      </c>
+      <c r="E5" s="16">
         <v>45821</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="26.4">
       <c r="B8" s="3">
-        <f>ROW()-7</f>
+        <f t="shared" ref="B8:B22" si="0">ROW()-7</f>
         <v>1</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="B9" s="3">
-        <f t="shared" ref="B9:B22" si="0">ROW()-7</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F9" s="3"/>
     </row>
@@ -1844,16 +1878,16 @@
         <v>3</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1862,13 +1896,13 @@
         <v>4</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F11" s="3"/>
     </row>
@@ -1878,16 +1912,16 @@
         <v>5</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="39.6">
@@ -1896,16 +1930,16 @@
         <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1914,13 +1948,13 @@
         <v>7</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F14" s="3"/>
     </row>
@@ -1930,16 +1964,16 @@
         <v>8</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="26.4">
@@ -1948,16 +1982,16 @@
         <v>9</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="2:6">
@@ -2057,7 +2091,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2065,10 +2099,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="E3" s="5">
         <v>45820</v>
@@ -2076,27 +2110,27 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="B5" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" s="5">
         <v>45821</v>
@@ -2104,37 +2138,37 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -2142,28 +2176,28 @@
         <v>1</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="L10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="52.8">
@@ -2171,40 +2205,40 @@
         <v>2</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="52.8">
       <c r="A12" s="3">
         <v>3</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>53</v>
+      <c r="B12" s="20" t="s">
+        <v>54</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E12" s="3">
         <v>255</v>
@@ -2212,14 +2246,14 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L12" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -2227,24 +2261,24 @@
         <v>4</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="L13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -2537,42 +2571,42 @@
     </row>
     <row r="30" spans="1:13">
       <c r="L30" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="L31" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="32" spans="1:13">
       <c r="M32" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33" spans="12:13">
       <c r="M33" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="34" spans="12:13">
       <c r="L34" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="35" spans="12:13">
       <c r="M35" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" spans="12:13">
       <c r="M36" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" spans="12:13">
       <c r="L38" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -2611,7 +2645,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -2619,10 +2653,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="E3" s="5">
         <v>45820</v>
@@ -2630,27 +2664,27 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="B5" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" s="5">
         <v>45821</v>
@@ -2658,37 +2692,37 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -2696,28 +2730,28 @@
         <v>1</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="L10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="52.8">
@@ -2725,26 +2759,28 @@
         <v>2</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="E11" s="3"/>
+        <v>56</v>
+      </c>
+      <c r="E11" s="3">
+        <v>255</v>
+      </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L11" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -2752,24 +2788,24 @@
         <v>3</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="L12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="52.8">
@@ -2777,26 +2813,26 @@
         <v>4</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L13" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -3089,42 +3125,42 @@
     </row>
     <row r="30" spans="1:13">
       <c r="L30" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="L31" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="32" spans="1:13">
       <c r="M32" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33" spans="12:13">
       <c r="M33" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="34" spans="12:13">
       <c r="L34" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="35" spans="12:13">
       <c r="M35" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" spans="12:13">
       <c r="M36" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="38" spans="12:13">
       <c r="L38" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -3163,7 +3199,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -3171,10 +3207,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="E3" s="5">
         <v>45820</v>
@@ -3182,54 +3218,54 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:12">
       <c r="B5" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L9" t="str">
         <f>"create table "&amp;C5&amp;" ("</f>
@@ -3598,7 +3634,7 @@
     </row>
     <row r="30" spans="1:12">
       <c r="L30" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -3638,7 +3674,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -3646,10 +3682,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="E3" s="5">
         <v>45820</v>
@@ -3657,71 +3693,71 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="16" t="s">
         <v>9</v>
       </c>
+      <c r="E4" s="15" t="s">
+        <v>10</v>
+      </c>
       <c r="L4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="B5" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="17">
+        <v>11</v>
+      </c>
+      <c r="E5" s="16">
         <v>45821</v>
       </c>
       <c r="L5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="13.8">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L9" s="11" t="s">
-        <v>52</v>
+        <v>16</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="13.8">
@@ -3729,28 +3765,28 @@
         <v>1</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E10" s="3">
         <v>255</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
-      <c r="L10" s="11" t="s">
-        <v>57</v>
+      <c r="L10" s="10" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="13.8">
@@ -3758,13 +3794,13 @@
         <v>2</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E11" s="3">
         <v>255</v>
@@ -3772,14 +3808,14 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="L11" s="11" t="s">
         <v>61</v>
+      </c>
+      <c r="L11" s="10" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="13.8">
@@ -3787,13 +3823,13 @@
         <v>3</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E12" s="3">
         <v>50</v>
@@ -3801,12 +3837,12 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
-      <c r="L12" s="11" t="s">
-        <v>64</v>
+      <c r="L12" s="10" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="56.25" customHeight="1">
@@ -3814,26 +3850,26 @@
         <v>4</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="L13" s="11" t="s">
         <v>69</v>
+      </c>
+      <c r="L13" s="10" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -3863,7 +3899,7 @@
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
-      <c r="L15" s="11"/>
+      <c r="L15" s="10"/>
     </row>
     <row r="16" spans="1:12" ht="13.8">
       <c r="A16" s="3">
@@ -3878,7 +3914,7 @@
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
-      <c r="L16" s="11"/>
+      <c r="L16" s="10"/>
     </row>
     <row r="17" spans="1:13" ht="13.8">
       <c r="A17" s="3">
@@ -3893,7 +3929,7 @@
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
-      <c r="L17" s="11"/>
+      <c r="L17" s="10"/>
     </row>
     <row r="18" spans="1:13" ht="13.8">
       <c r="A18" s="3">
@@ -3908,7 +3944,7 @@
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
-      <c r="L18" s="11"/>
+      <c r="L18" s="10"/>
     </row>
     <row r="19" spans="1:13" ht="13.8">
       <c r="A19" s="3">
@@ -3923,7 +3959,7 @@
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
-      <c r="L19" s="11"/>
+      <c r="L19" s="10"/>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="3">
@@ -4095,81 +4131,81 @@
     </row>
     <row r="30" spans="1:13">
       <c r="L30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="L31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:13">
       <c r="M32" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" spans="12:13">
       <c r="M33" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34" spans="12:13">
       <c r="L34" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:13">
       <c r="A49" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D50" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14"/>
+        <v>63</v>
+      </c>
+      <c r="D50" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13"/>
+      <c r="H50" s="13"/>
+      <c r="I50" s="13"/>
+      <c r="J50" s="13"/>
     </row>
     <row r="51" spans="1:13">
       <c r="A51" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B51" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C51" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D51" t="s">
-        <v>79</v>
-      </c>
-      <c r="M51" s="10"/>
+        <v>80</v>
+      </c>
+      <c r="M51" s="9"/>
     </row>
     <row r="52" spans="1:13">
       <c r="A52" t="s">
+        <v>81</v>
+      </c>
+      <c r="B52" t="s">
+        <v>82</v>
+      </c>
+      <c r="C52" t="s">
+        <v>83</v>
+      </c>
+      <c r="D52" t="s">
         <v>80</v>
-      </c>
-      <c r="B52" t="s">
-        <v>81</v>
-      </c>
-      <c r="C52" t="s">
-        <v>82</v>
-      </c>
-      <c r="D52" t="s">
-        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -4209,7 +4245,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -4217,10 +4253,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="E3" s="5">
         <v>45820</v>
@@ -4228,61 +4264,61 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:12">
       <c r="B5" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -4290,28 +4326,28 @@
         <v>1</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="L10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -4319,13 +4355,13 @@
         <v>2</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E11" s="3">
         <v>10</v>
@@ -4333,12 +4369,12 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="L11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -4667,12 +4703,12 @@
     </row>
     <row r="30" spans="1:12">
       <c r="L30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="L31" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -4711,7 +4747,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -4719,10 +4755,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="E3" s="5">
         <v>45820</v>
@@ -4730,65 +4766,65 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="16" t="s">
         <v>9</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="B5" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="17">
+        <v>11</v>
+      </c>
+      <c r="E5" s="16">
         <v>45821</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -4796,28 +4832,28 @@
         <v>1</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="L10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -4825,13 +4861,13 @@
         <v>2</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E11" s="3">
         <v>10</v>
@@ -4839,12 +4875,12 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="L11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="52.8">
@@ -4852,13 +4888,13 @@
         <v>3</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -4866,10 +4902,10 @@
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -5180,27 +5216,27 @@
     </row>
     <row r="30" spans="1:13">
       <c r="L30" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="L31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32" spans="1:13">
       <c r="M32" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33" spans="12:13">
       <c r="M33" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35" spans="12:13">
       <c r="L35" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -5211,7 +5247,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A892FE8F-F716-484E-9AB0-36CC9F272280}">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
     <col min="2" max="2" width="16.109375" customWidth="1"/>
@@ -5239,7 +5275,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -5247,10 +5283,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="E3" s="5">
         <v>45820</v>
@@ -5258,61 +5294,61 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:12">
       <c r="B5" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -5320,28 +5356,28 @@
         <v>1</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="L10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -5349,13 +5385,13 @@
         <v>2</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E11" s="3">
         <v>10</v>
@@ -5363,12 +5399,12 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="L11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -5376,13 +5412,13 @@
         <v>3</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E12" s="3">
         <v>1</v>
@@ -5390,12 +5426,14 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
+      <c r="J12" s="3" t="s">
+        <v>106</v>
+      </c>
       <c r="L12" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -5705,13 +5743,13 @@
       </c>
     </row>
     <row r="30" spans="1:12" ht="18">
-      <c r="L30" s="12" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12">
-      <c r="L31" t="s">
-        <v>49</v>
+      <c r="L30" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="L32" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -5750,7 +5788,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -5758,10 +5796,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="E3" s="5">
         <v>45820</v>
@@ -5769,65 +5807,65 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="16" t="s">
         <v>9</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="B5" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="17">
+        <v>11</v>
+      </c>
+      <c r="E5" s="16">
         <v>45821</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -5835,28 +5873,28 @@
         <v>1</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="L10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="52.8">
@@ -5864,13 +5902,13 @@
         <v>2</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E11" s="3">
         <v>255</v>
@@ -5878,14 +5916,14 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L11" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -5893,13 +5931,13 @@
         <v>3</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E12" s="3">
         <v>255</v>
@@ -5910,7 +5948,7 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="L12" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="26.4">
@@ -5918,13 +5956,13 @@
         <v>4</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E13" s="3">
         <v>255</v>
@@ -5934,10 +5972,10 @@
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="L13" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -5945,24 +5983,24 @@
         <v>5</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="L14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -5970,24 +6008,24 @@
         <v>6</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="L15" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="52.8">
@@ -5995,26 +6033,26 @@
         <v>7</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L16" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -6022,13 +6060,13 @@
         <v>8</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E17" s="3">
         <v>255</v>
@@ -6039,7 +6077,7 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="L17" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -6047,13 +6085,13 @@
         <v>9</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -6062,7 +6100,7 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="L18" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="52.8">
@@ -6070,13 +6108,13 @@
         <v>10</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -6084,10 +6122,10 @@
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="8" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L19" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -6095,25 +6133,27 @@
         <v>11</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E20" s="3"/>
+        <v>56</v>
+      </c>
+      <c r="E20" s="3">
+        <v>255</v>
+      </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
       <c r="L20" t="str">
         <f>C20&amp;" "&amp;D20&amp;" "&amp;IF(E20&lt;&gt;"","("&amp;E20&amp;")","")&amp;IF(C21&lt;&gt;"",",","")</f>
-        <v>photo1 BLOB ,</v>
+        <v>photo1 VARCHAR (255),</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -6121,25 +6161,27 @@
         <v>12</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E21" s="3"/>
+        <v>56</v>
+      </c>
+      <c r="E21" s="3">
+        <v>255</v>
+      </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="L21" t="str">
         <f>C21&amp;" "&amp;D21&amp;" "&amp;IF(E21&lt;&gt;"","("&amp;E21&amp;")","")&amp;IF(C22&lt;&gt;"",",","")</f>
-        <v>photo2 BLOB ,</v>
+        <v>photo2 VARCHAR (255),</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -6147,25 +6189,27 @@
         <v>13</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E22" s="3"/>
+        <v>56</v>
+      </c>
+      <c r="E22" s="3">
+        <v>255</v>
+      </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="L22" t="str">
         <f>C22&amp;" "&amp;D22&amp;" "&amp;IF(E22&lt;&gt;"","("&amp;E22&amp;")","")&amp;IF(C23&lt;&gt;"",",","")</f>
-        <v>photo3 BLOB ,</v>
+        <v>photo3 VARCHAR (255),</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -6173,25 +6217,27 @@
         <v>14</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E23" s="3"/>
+        <v>56</v>
+      </c>
+      <c r="E23" s="3">
+        <v>255</v>
+      </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="L23" t="str">
         <f>C23&amp;" "&amp;D23&amp;" "&amp;IF(E23&lt;&gt;"","("&amp;E23&amp;")","")&amp;IF(C24&lt;&gt;"",",","")</f>
-        <v>photo4 BLOB ,</v>
+        <v>photo4 VARCHAR (255),</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -6199,24 +6245,26 @@
         <v>15</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E24" s="3"/>
+        <v>56</v>
+      </c>
+      <c r="E24" s="3">
+        <v>255</v>
+      </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="L24" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -6310,58 +6358,58 @@
       </c>
     </row>
     <row r="30" spans="1:13" ht="18">
-      <c r="L30" s="12" t="s">
-        <v>151</v>
+      <c r="L30" s="11" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="L31" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="32" spans="1:13">
       <c r="M32" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33" spans="12:13">
       <c r="M33" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="34" spans="12:13">
       <c r="L34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="12:13">
       <c r="M35" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" spans="12:13">
       <c r="M36" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="37" spans="12:13">
       <c r="L37" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="38" spans="12:13">
       <c r="M38" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="39" spans="12:13">
       <c r="M39" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41" spans="12:13">
       <c r="L41" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -6400,7 +6448,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -6408,10 +6456,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="E3" s="5">
         <v>45820</v>
@@ -6419,27 +6467,27 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="B5" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" s="5">
         <v>45821</v>
@@ -6447,37 +6495,37 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -6485,28 +6533,28 @@
         <v>1</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="L10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="52.8">
@@ -6514,13 +6562,13 @@
         <v>2</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E11" s="3">
         <v>255</v>
@@ -6528,14 +6576,14 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="52.8">
@@ -6543,26 +6591,26 @@
         <v>3</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -6570,13 +6618,13 @@
         <v>4</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E13" s="3">
         <v>50</v>
@@ -6587,7 +6635,7 @@
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="L13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -6595,13 +6643,13 @@
         <v>5</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -6610,7 +6658,7 @@
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="L14" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -6627,7 +6675,7 @@
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="L15" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:12">
@@ -6644,7 +6692,7 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
       <c r="L16" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -6882,43 +6930,43 @@
       </c>
     </row>
     <row r="30" spans="1:13" ht="18">
-      <c r="L30" s="12" t="s">
-        <v>164</v>
+      <c r="L30" s="11" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="L31" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="32" spans="1:13">
       <c r="M32" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33" spans="12:13">
       <c r="M33" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="34" spans="12:13">
       <c r="L34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="12:13">
       <c r="M35" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" spans="12:13">
       <c r="M36" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" spans="12:13">
       <c r="L38" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -6957,7 +7005,7 @@
         <v>3</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -6965,10 +7013,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>7</v>
       </c>
       <c r="E3" s="5">
         <v>45820</v>
@@ -6976,61 +7024,61 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:12">
       <c r="B5" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -7038,28 +7086,28 @@
         <v>1</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="L10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -7067,13 +7115,13 @@
         <v>2</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E11" s="3">
         <v>20</v>
@@ -7081,12 +7129,12 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
       <c r="L11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -7094,24 +7142,26 @@
         <v>3</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E12" s="3"/>
+        <v>56</v>
+      </c>
+      <c r="E12" s="3">
+        <v>255</v>
+      </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="L12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -7421,13 +7471,13 @@
       </c>
     </row>
     <row r="30" spans="1:12">
-      <c r="L30" s="13" t="s">
-        <v>175</v>
+      <c r="L30" s="12" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="L32" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
